--- a/translation/review/000scriptAKYO_0030A.xlsx
+++ b/translation/review/000scriptAKYO_0030A.xlsx
@@ -16,7 +16,7 @@
     <t>The True Little Sister Showdown : Siscalypse</t>
   </si>
   <si>
-    <t>El Verdadero Enfrentamiento de Hermanitas: Siscalipse</t>
+    <t>El Verdadero Enfrentamiento de Hermanitas:＿Siscalipse</t>
   </si>
   <si>
     <t>Kirino</t>
@@ -25,7 +25,7 @@
     <t>Although God Eater is super interesting, I didn't call you all here today just to play multiplayer.</t>
   </si>
   <si>
-    <t>Aunque God Eater es súper interesante, no los llamé hoy solo para jugar multijugador.</t>
+    <t>Aunque God Eater es súper interesante, no los＿llamé hoy solo para jugar multijugador.</t>
   </si>
   <si>
     <t>Kuroneko</t>
@@ -34,7 +34,7 @@
     <t>Oh, is that so? Then what is your reason for calling us here then? Please do explain.</t>
   </si>
   <si>
-    <t>Oh, ¿eso crees? Entonces, ¿cuál es tu razón para llamarnos? Por favor, explícate.</t>
+    <t>Oh, ¿eso crees? Entonces, ¿cuál es tu razón para＿llamarnos? Por favor, explícate.</t>
   </si>
   <si>
     <t>Tadah!</t>
@@ -67,19 +67,19 @@
     <t>"Siscaly" -- Official title is Shin Imouto Taisen Siscalypse (The True Little Sister Showdown : Siscalypse)</t>
   </si>
   <si>
-    <t>«Siscaly» -- El título oficial es Shin Imouto Taisen Siscalypse (El Verdadero Enfrentamiento de Hermanitas: Siscalipse)</t>
+    <t>«Siscaly» -- El título oficial es Shin Imouto Taisen＿Siscalypse (El Verdadero Enfrentamiento de＿Hermanitas: Siscalipse)</t>
   </si>
   <si>
     <t>Although it looks like an adventure game, it's actually a game where you train your "little sister", and pit her against others online.</t>
   </si>
   <si>
-    <t>Aunque parece un juego de aventuras, en realidad es un juego donde entrenas a tu «hermanita» y la enfrentas contra otras en línea.</t>
+    <t>Aunque parece un juego de aventuras, en realidad＿es un juego donde entrenas a tu «hermanita» y＿la enfrentas contra otras en línea.</t>
   </si>
   <si>
     <t>And also, the girl who loses in battle will have their costume ripped up in a shameful way...</t>
   </si>
   <si>
-    <t>Y además, la chica que pierde en la batalla tendrá su disfraz destrozado de manera vergonzosa...</t>
+    <t>Y además, la chica que pierde en la batalla tendrá＿su disfraz destrozado de manera vergonzosa...</t>
   </si>
   <si>
     <t>Kirino loves that game.</t>
@@ -94,7 +94,7 @@
     <t>What about "Siscaly"? Do you want everyone to play against each other?</t>
   </si>
   <si>
-    <t>¿Qué hay con «Siscaly»? ¿Quieres que todos jueguen entre sí?</t>
+    <t>¿Qué hay con «Siscaly»? ¿Quieres que todos＿jueguen entre sí?</t>
   </si>
   <si>
     <t>Ehehe, it's a little different...</t>
@@ -118,7 +118,7 @@
     <t>Yeah! It's a tournament to gather every player across the country with confidence in their skills and decide who is the strongest little sister user!</t>
   </si>
   <si>
-    <t>¡Sí! ¡Es un torneo para reunir a todos los jugadores del país con confianza en sus habilidades y decidir quién es el usuario de hermanitas más fuerte!</t>
+    <t>¡Sí! ¡Es un torneo para reunir a todos los＿jugadores del país con confianza en sus[habilidades y decidir quién es el usuario de＿hermanitas más fuerte!]</t>
   </si>
   <si>
     <t>It's a tournament made just for me!</t>
@@ -136,19 +136,19 @@
     <t>We're here today to practice for this tournament!</t>
   </si>
   <si>
-    <t>¡Estamos aquí hoy para practicar para este torneo!</t>
+    <t>¡Estamos aquí hoy para practicar para este＿torneo!</t>
   </si>
   <si>
     <t>If thou speak about that tournament, I also have some knowledge.</t>
   </si>
   <si>
-    <t>Si hablas de ese torneo, yo también tengo algo de conocimiento.</t>
+    <t>Si hablas de ese torneo, yo también tengo algo＿de conocimiento.</t>
   </si>
   <si>
     <t>It is said that the winner will be awarded a prize from the organizers.</t>
   </si>
   <si>
-    <t>Se dice que el ganador recibirá un premio de parte de los organizadores.</t>
+    <t>Se dice que el ganador recibirá un premio de＿parte de los organizadores.</t>
   </si>
   <si>
     <t>*gulp*</t>
@@ -163,13 +163,13 @@
     <t>Kirino and Kuroneko... It appears they are both "very VERY interested" in the tournament prize.</t>
   </si>
   <si>
-    <t>Kirino y Kuroneko... Parece que ambas están «muy MUY interesadas» en el premio del torneo.</t>
+    <t>Kirino y Kuroneko... Parece que ambas están «muy＿MUY interesadas» en el premio del torneo.</t>
   </si>
   <si>
     <t>While those two are usually on bad terms, this time it seems they share a common objective.</t>
   </si>
   <si>
-    <t>Aunque esas dos normalmente están en malos términos, esta vez parece que comparten un objetivo común.</t>
+    <t>Aunque esas dos normalmente están en malos＿términos, esta vez parece que comparten un＿objetivo común.</t>
   </si>
   <si>
     <t>...Eh? The thing that just flashed by?!</t>
@@ -181,25 +181,25 @@
     <t>?! And inside my head the "Siscaly Game Tournament" keyword is stuck and refuses to let go...</t>
   </si>
   <si>
-    <t>¡?! Y dentro de mi cabeza la palabra clave «Torneo del Juego Siscaly» está atascada y se niega a soltarse...</t>
+    <t>¡?! Y dentro de mi cabeza la palabra clave «Torneo＿del Juego Siscaly» está atascada y se niega a＿soltarse...</t>
   </si>
   <si>
     <t>It's the same as with the "Two-Shot Conversation"; it feels like I'm playing a game.</t>
   </si>
   <si>
-    <t>Es lo mismo que con la «Conversación a Dueto»; siento como si estuviera jugando un juego.</t>
+    <t>Es lo mismo que con la «Conversación a Dueto»;＿siento como si estuviera jugando un juego.</t>
   </si>
   <si>
     <t>I'm a third year high schooler, not a chuuni! Thanks to them, my peaceful ordinary life got corrupted by irrational eccentricity...</t>
   </si>
   <si>
-    <t>Soy un estudiante de tercer año de preparatoria, ¡no un chuuni! Gracias a ellos, mi pacífica vida ordinaria se corrompió con excentricidades irracionales...</t>
+    <t>Soy un estudiante de tercer año de preparatoria,＿¡no un chuuni! Gracias a ellos, mi pacífica vida[ordinaria se corrompió con excentricidades＿irracionales...]</t>
   </si>
   <si>
     <t>Okay, the exact name of this system will be: O.R.E. System. (Order.Record.Effect)</t>
   </si>
   <si>
-    <t>De acuerdo, el nombre exacto de este sistema será: Sistema O.R.E. (Order.Record.Effect)</t>
+    <t>De acuerdo, el nombre exacto de este sistema＿será: Sistema O.R.E. (Order.Record.Effect)</t>
   </si>
   <si>
     <t>This being said...</t>
@@ -217,7 +217,7 @@
     <t>So you can make a good proposal after all.</t>
   </si>
   <si>
-    <t>Así que al final sí puedes hacer una buena propuesta.</t>
+    <t>Así que al final sí puedes hacer una buena＿propuesta.</t>
   </si>
   <si>
     <t>Kiririn-shi, Tis be a nice idea!</t>
@@ -241,31 +241,31 @@
     <t>Why do even I have to... Wait, hold on?!</t>
   </si>
   <si>
-    <t>¿Por qué incluso yo tengo que...? ¡Espera, un momento?!</t>
+    <t>¿Por qué incluso yo tengo que...? ¡Espera, un＿momento?!</t>
   </si>
   <si>
     <t>There's something on the upper-left that's bothering me... Is that the ability of the O.R.E system?</t>
   </si>
   <si>
-    <t>Hay algo en la parte superior izquierda que me molesta... ¿Es esa la habilidad del sistema O.R.E?</t>
+    <t>Hay algo en la parte superior izquierda que me＿molesta... ¿Es esa la habilidad del sistema O.R.E?</t>
   </si>
   <si>
     <t>With the almighty power to manipulate and control everything at hand... Is this the new power I was blessed with?</t>
   </si>
   <si>
-    <t>Con el poder todopoderoso de manipular y controlar todo a mi alcance... ¿Es este el nuevo poder con el que fui bendecido?</t>
+    <t>Con el poder todopoderoso de manipular y＿controlar todo a mi alcance... ¿Es este el nuevo＿poder con el que fui bendecido?</t>
   </si>
   <si>
     <t>Oh well, I'll put these Chuuni delusions aside. If I want to join the tournament, I'll just have to select it.</t>
   </si>
   <si>
-    <t>Bueno, dejaré de lado estos delirios chuuni. Si quiero unirme al torneo, solo tendré que seleccionarlo.</t>
+    <t>Bueno, dejaré de lado estos delirios chuuni. Si＿quiero unirme al torneo, solo tendré que＿seleccionarlo.</t>
   </si>
   <si>
     <t>Which means I'll have to take part in it too?!</t>
   </si>
   <si>
-    <t>¡¿Lo que significa que yo también tendré que participar?!</t>
+    <t>¡¿Lo que significa que yo también tendré que＿participar?!</t>
   </si>
   <si>
     <t>Isn't that obvious? What are you saying?</t>
@@ -277,19 +277,19 @@
     <t>That means if I perchance happen to win the tournament, I would get the rights to receive the 【tournament's prize】 as well?</t>
   </si>
   <si>
-    <t>Eso significa que si por casualidad gano el torneo, también tendría derecho a recibir el 【premio del torneo】, ¿no?</t>
+    <t>Eso significa que si por casualidad gano el＿torneo, también tendría derecho a recibir el＿【premio del torneo】, ¿no?</t>
   </si>
   <si>
     <t>Eh? You're also interested in the Siscaly goods?</t>
   </si>
   <si>
-    <t>¿Eh? ¿También te interesan los productos de Siscaly?</t>
+    <t>¿Eh? ¿También te interesan los productos de＿Siscaly?</t>
   </si>
   <si>
     <t>Aha, I see. Did you also awaken to the "moe of little sisters"?</t>
   </si>
   <si>
-    <t>Aha, ya veo. ¿También despertaste al «moe de las hermanitas»?</t>
+    <t>Aha, ya veo. ¿También despertaste al «moe de＿las hermanitas»?</t>
   </si>
   <si>
     <t>...Of course not.</t>
@@ -307,7 +307,7 @@
     <t>Nothing. Everyone joins the Siscaly tournament. That's a fun project.</t>
   </si>
   <si>
-    <t>Nada. Todos se unen al torneo de Siscaly. Eso es un proyecto divertido.</t>
+    <t>Nada. Todos se unen al torneo de Siscaly. Eso＿es un proyecto divertido.</t>
   </si>
   <si>
     <t>Hehe, isn't it?</t>
@@ -337,7 +337,7 @@
     <t>You're all joining the tournament for the prizes, right?</t>
   </si>
   <si>
-    <t>Todos se unen al torneo por los premios, ¿verdad?</t>
+    <t>Todos se unen al torneo por los premios,＿¿verdad?</t>
   </si>
   <si>
     <t>Obviously.</t>
@@ -349,31 +349,31 @@
     <t>But if a beginner like me were to participate, I'd be nothing more than a burden.</t>
   </si>
   <si>
-    <t>Pero si un principiante como yo participara, no sería más que una carga.</t>
+    <t>Pero si un principiante como yo participara, no＿sería más que una carga.</t>
   </si>
   <si>
     <t>There's no need to purposefully reduce your chances of winning.</t>
   </si>
   <si>
-    <t>No hay necesidad de reducir a propósito sus posibilidades de ganar.</t>
+    <t>No hay necesidad de reducir a propósito sus＿posibilidades de ganar.</t>
   </si>
   <si>
     <t>That won't be a problem if you undergo special training.</t>
   </si>
   <si>
-    <t>Eso no será un problema si te sometes a un entrenamiento especial.</t>
+    <t>Eso no será un problema si te sometes a un＿entrenamiento especial.</t>
   </si>
   <si>
     <t>The opponents are gamers with lots of experience, right? I don't think that last minute training will somehow do it.</t>
   </si>
   <si>
-    <t>Los oponentes son jugadores con mucha experiencia, ¿verdad? No creo que un entrenamiento de última hora lo logre.</t>
+    <t>Los oponentes son jugadores con mucha＿experiencia, ¿verdad? No creo que un＿entrenamiento de última hora lo logre.</t>
   </si>
   <si>
     <t>Even if I do get better at the game, I feel that it'd be rude to those who really like Siscaly.</t>
   </si>
   <si>
-    <t>Incluso si mejoro en el juego, siento que sería una falta de respeto para quienes realmente aman Siscaly.</t>
+    <t>Incluso si mejoro en el juego, siento que sería＿una falta de respeto para quienes realmente＿aman Siscaly.</t>
   </si>
   <si>
     <t>...What do you mean?</t>
@@ -391,7 +391,7 @@
     <t>If someone, who doesn't like little sisters at all, were to quickly complete a really heart-wrecking little sister game and said it's a shitty game, how would</t>
   </si>
   <si>
-    <t>Si alguien a quien no le gustan las hermanitas en absoluto completara rápidamente un juego de hermanitas desgarrador y dijera que es un juego de mierda, ¿cómo te</t>
+    <t>Si alguien a quien no le gustan las hermanitas＿en absoluto completara rápidamente un juego[de hermanitas desgarrador y dijera que es un＿juego de mierda, ¿cómo te]</t>
   </si>
   <si>
     <t>you feel?</t>
@@ -412,7 +412,7 @@
     <t>I'm not a Siscaly fan, and if I were to take part at the Siscaly tournament and win, it'd be rude to real Siscaly fans.</t>
   </si>
   <si>
-    <t>No soy fan de Siscaly, y si participara en el torneo de Siscaly y ganara, sería una falta de respeto hacia los verdaderos fans de Siscaly.</t>
+    <t>No soy fan de Siscaly, y si participara en el＿torneo de Siscaly y ganara, sería una falta de＿respeto hacia los verdaderos fans de Siscaly.</t>
   </si>
   <si>
     <t>B-But...</t>
@@ -424,25 +424,25 @@
     <t>Kiririn-shi, what Kyousuke-shi said is justified.</t>
   </si>
   <si>
-    <t>Kiririn-shi, lo que dijo Kyousuke-shi es justificable.</t>
+    <t>Kiririn-shi, lo que dijo Kyousuke-shi es＿justificable.</t>
   </si>
   <si>
     <t>But, the tournament requires two people sets to take part... now we're one too many...</t>
   </si>
   <si>
-    <t>Pero, el torneo requiere equipos de dos personas... ahora somos uno de más...</t>
+    <t>Pero, el torneo requiere equipos de dos＿personas... ahora somos uno de más...</t>
   </si>
   <si>
     <t>If that's the case, how about we get a member from the SNS?</t>
   </si>
   <si>
-    <t>Si ese es el caso, ¿qué tal si conseguimos un miembro de las redes sociales?</t>
+    <t>Si ese es el caso, ¿qué tal si conseguimos un＿miembro de las redes sociales?</t>
   </si>
   <si>
     <t>Of course, I wouldst be happier if thou were to take part as well, Kyousuke-shi...</t>
   </si>
   <si>
-    <t>Por supuesto, sería más feliz si tú también participaras, Kyousuke-shi...</t>
+    <t>Por supuesto, sería más feliz si tú también＿participaras, Kyousuke-shi...</t>
   </si>
   <si>
     <t>You are not coming?</t>
@@ -469,7 +469,7 @@
     <t>Sorry, Kirino. Even though you took the effort to invite me.</t>
   </si>
   <si>
-    <t>Lo siento, Kirino. Aunque te tomaste la molestia de invitarme.</t>
+    <t>Lo siento, Kirino. Aunque te tomaste la molestia＿de invitarme.</t>
   </si>
   <si>
     <t>...Hmph.</t>
@@ -478,13 +478,13 @@
     <t>No big deal. Besides, wouldn't it be easier with one less person in the special training?</t>
   </si>
   <si>
-    <t>No es gran cosa. Además, ¿no sería más fácil con una persona menos en el entrenamiento especial?</t>
+    <t>No es gran cosa. Además, ¿no sería más fácil＿con una persona menos en el entrenamiento＿especial?</t>
   </si>
   <si>
     <t>I see. Kiririn-shi wanted to take part in the tournament together with Kyousuke-shi.</t>
   </si>
   <si>
-    <t>Ya veo. Kiririn-shi quería participar en el torneo junto con Kyousuke-shi.</t>
+    <t>Ya veo. Kiririn-shi quería participar en el torneo＿junto con Kyousuke-shi.</t>
   </si>
   <si>
     <t>Huh? Don't be mistaken. No one said such a thing.</t>
@@ -496,7 +496,7 @@
     <t>I see, I see? Being unable to play together with me makes you that sad!</t>
   </si>
   <si>
-    <t>¿Ya veo, ya veo? ¡No poder jugar conmigo te pone tan triste!</t>
+    <t>¿Ya veo, ya veo? ¡No poder jugar conmigo te＿pone tan triste!</t>
   </si>
   <si>
     <t>Gross! Like hell it would!</t>
@@ -514,7 +514,7 @@
     <t>Shut up! Everyone who's not taking part in the tournament, get out of the room immediately!</t>
   </si>
   <si>
-    <t>¡Cállate! ¡Todos los que no participen en el torneo, salgan del cuarto de inmediato!</t>
+    <t>¡Cállate! ¡Todos los que no participen en el＿torneo, salgan del cuarto de inmediato!</t>
   </si>
   <si>
     <t>Yes, yes...</t>
@@ -526,25 +526,25 @@
     <t>With those three confined in the same room, I can't think it'll end without something bad happening.</t>
   </si>
   <si>
-    <t>Con esas tres encerradas en el mismo cuarto, no puedo pensar que terminará sin que algo malo ocurra.</t>
+    <t>Con esas tres encerradas en el mismo cuarto, no＿puedo pensar que terminará sin que algo malo＿ocurra.</t>
   </si>
   <si>
     <t>Especially Kirino and Kuroneko. If it's about victory or defeat, any mistakes and they'll be out for each other's blood.</t>
   </si>
   <si>
-    <t>Especialmente Kirino y Kuroneko. Cuando se trata de victoria o derrota, cualquier error y se lanzarán a la yugular.</t>
+    <t>Especialmente Kirino y Kuroneko. Cuando se trata＿de victoria o derrota, cualquier error y se＿lanzarán a la yugular.</t>
   </si>
   <si>
     <t>Well then, if we waste our time on quarreling, our chances of winning will decrease!</t>
   </si>
   <si>
-    <t>¡Bueno, si perdemos el tiempo discutiendo, nuestras posibilidades de ganar disminuirán!</t>
+    <t>¡Bueno, si perdemos el tiempo discutiendo,＿nuestras posibilidades de ganar disminuirán!</t>
   </si>
   <si>
     <t>'Tis practice time! Our Siscaly training starts immediately!</t>
   </si>
   <si>
-    <t>¡Es hora de practicar! ¡Nuestro entrenamiento de Siscaly comienza de inmediato!</t>
+    <t>¡Es hora de practicar! ¡Nuestro entrenamiento de＿Siscaly comienza de inmediato!</t>
   </si>
   <si>
     <t>Understood...</t>
@@ -562,13 +562,13 @@
     <t>Leave your little sister to us; Senpai only needs to wait for news of victory.</t>
   </si>
   <si>
-    <t>Déjanos a tu hermanita; Senpai solo necesita esperar noticias de la victoria.</t>
+    <t>Déjanos a tu hermanita; Senpai solo necesita＿esperar noticias de la victoria.</t>
   </si>
   <si>
     <t>You will forever regret not participating, but do look forward to hearing our exploits.</t>
   </si>
   <si>
-    <t>Te arrepentirás para siempre de no participar, pero espera con ansias escuchar nuestras hazañas.</t>
+    <t>Te arrepentirás para siempre de no participar,＿pero espera con ansias escuchar nuestras＿hazañas.</t>
   </si>
   <si>
     <t>Yeah, I'm looking forward to them.</t>
@@ -598,19 +598,19 @@
     <t>With my current skills, won't I just embarrass myself in front of others?</t>
   </si>
   <si>
-    <t>Con mis habilidades actuales, ¿no terminaré avergonzándome frente a los demás?</t>
+    <t>Con mis habilidades actuales, ¿no terminaré＿avergonzándome frente a los demás?</t>
   </si>
   <si>
     <t>I don't mind losing, but they would become VERY devastated.</t>
   </si>
   <si>
-    <t>No me importa perder, pero ellas quedarían MUY devastadas.</t>
+    <t>No me importa perder, pero ellas quedarían MUY＿devastadas.</t>
   </si>
   <si>
     <t>I don't want to bring them down by participating in the tournament, but there's no good reason to refuse...</t>
   </si>
   <si>
-    <t>No quiero defraudarlas participando en el torneo, pero no hay una buena razón para rechazar...</t>
+    <t>No quiero defraudarlas participando en el torneo,＿pero no hay una buena razón para rechazar...</t>
   </si>
 </sst>
 </file>
